--- a/P2 Reproducao/dados/dados.xlsx
+++ b/P2 Reproducao/dados/dados.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marmello/Documents/Ensino/Ecologia Animal/Praticas/EcoAnimal/P2 Reproducao/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01534983-824E-3F44-9657-B59DD374200C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC6F65C6-079F-8D45-B595-989F19AD48CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="metadata1" sheetId="3" r:id="rId1"/>
-    <sheet name="metadata2" sheetId="4" r:id="rId2"/>
+    <sheet name="metadata (originais)" sheetId="3" r:id="rId1"/>
+    <sheet name="metadata2 (adicionados)" sheetId="4" r:id="rId2"/>
     <sheet name="narwhal" sheetId="5" r:id="rId3"/>
     <sheet name="sex" sheetId="6" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="Excel_BuiltIn__FilterDatabase">#REF!</definedName>
-    <definedName name="nde_dryad_s1rn8pk43" localSheetId="0">metadata1!#REF!</definedName>
-    <definedName name="nde_dryad_s1rn8pk43_1" localSheetId="0">metadata1!$A$1:$AX$2</definedName>
+    <definedName name="nde_dryad_s1rn8pk43" localSheetId="0">'metadata (originais)'!#REF!</definedName>
+    <definedName name="nde_dryad_s1rn8pk43_1" localSheetId="0">'metadata (originais)'!$A$1:$AX$2</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1435" uniqueCount="209">
   <si>
     <t>IDNO</t>
   </si>
@@ -637,9 +637,6 @@
     <t>BODY</t>
   </si>
   <si>
-    <t>Tail length</t>
-  </si>
-  <si>
     <t>1=F, 2=M</t>
   </si>
   <si>
@@ -707,6 +704,18 @@
   </si>
   <si>
     <t>Scoresbysund_kap_tobin_(iskant)</t>
+  </si>
+  <si>
+    <t>Tusk length (cm)</t>
+  </si>
+  <si>
+    <t>Obs: Estes metados não estavam disponíveis no suplemento original e tiveram que ser esclarecidos com os autores do artigo.</t>
+  </si>
+  <si>
+    <t>Tail width (cm) (fluke)</t>
+  </si>
+  <si>
+    <t>Tail length (cm) (fluke)</t>
   </si>
 </sst>
 </file>
@@ -1642,7 +1651,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CACB93EF-0290-D848-BAE9-63F27AC6C2C8}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="10.75" style="8"/>
@@ -1651,61 +1660,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="7" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="8" t="s">
+    <row r="4" spans="1:2">
+      <c r="A4" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B4" s="8" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>184</v>
+    <row r="6" spans="1:2">
+      <c r="A6" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="7" t="s">
-        <v>178</v>
+      <c r="A7" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="8" t="s">
-        <v>175</v>
+        <v>3</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>5</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>180</v>
+      <c r="A10" s="7" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="8" t="s">
-        <v>12</v>
+        <v>175</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>182</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -1802,7 +1848,7 @@
         <v>23</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H2" s="14">
         <v>3971</v>
@@ -1954,7 +2000,7 @@
       </c>
       <c r="F6" s="12"/>
       <c r="G6" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H6" s="14">
         <v>3980</v>
@@ -1993,7 +2039,7 @@
         <v>22</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H7" s="14">
         <v>3980</v>
@@ -2030,7 +2076,7 @@
         <v>14</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H8" s="14">
         <v>3980</v>
@@ -2328,7 +2374,7 @@
         <v>17</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H16" s="14"/>
       <c r="I16" s="14">
@@ -2365,7 +2411,7 @@
         <v>17</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H17" s="14"/>
       <c r="I17" s="14">
@@ -2556,7 +2602,7 @@
         <v>22</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H22" s="14">
         <v>3980</v>
@@ -3014,7 +3060,7 @@
         <v>28</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H34" s="12">
         <v>3971</v>
@@ -3051,7 +3097,7 @@
         <v>29</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H35" s="14">
         <v>3980</v>
@@ -3170,7 +3216,7 @@
         <v>12</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H38" s="14">
         <v>3980</v>
@@ -3441,7 +3487,7 @@
         <v>24</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H45" s="12">
         <v>99</v>
@@ -3480,7 +3526,7 @@
         <v>11</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H46" s="14">
         <v>3980</v>
@@ -3774,7 +3820,7 @@
         <v>14</v>
       </c>
       <c r="G54" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H54" s="12">
         <v>3971</v>
@@ -3813,7 +3859,7 @@
         <v>20</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H55" s="12">
         <v>3971</v>
@@ -4010,7 +4056,7 @@
         <v>10</v>
       </c>
       <c r="G60" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H60" s="14">
         <v>3980</v>
@@ -4281,7 +4327,7 @@
         <v>14</v>
       </c>
       <c r="G67" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H67" s="14">
         <v>3980</v>
@@ -4355,7 +4401,7 @@
         <v>2</v>
       </c>
       <c r="G69" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H69" s="14">
         <v>3980</v>
@@ -4476,7 +4522,7 @@
         <v>14</v>
       </c>
       <c r="G72" s="13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H72" s="14">
         <v>3971</v>
@@ -4548,7 +4594,7 @@
       </c>
       <c r="F74" s="12"/>
       <c r="G74" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H74" s="12">
         <v>3971</v>
@@ -4624,7 +4670,7 @@
         <v>2</v>
       </c>
       <c r="G76" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H76" s="12">
         <v>3971</v>
@@ -4747,7 +4793,7 @@
         <v>21</v>
       </c>
       <c r="G79" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H79" s="12">
         <v>99</v>
@@ -5096,7 +5142,7 @@
         <v>31</v>
       </c>
       <c r="G88" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H88" s="14">
         <v>3980</v>
@@ -5289,7 +5335,7 @@
         <v>14</v>
       </c>
       <c r="G93" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H93" s="12">
         <v>3971</v>
@@ -5328,7 +5374,7 @@
         <v>28</v>
       </c>
       <c r="G94" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H94" s="14">
         <v>3971</v>
@@ -5445,7 +5491,7 @@
         <v>11</v>
       </c>
       <c r="G97" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H97" s="14">
         <v>3980</v>
@@ -5484,7 +5530,7 @@
         <v>2</v>
       </c>
       <c r="G98" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H98" s="14">
         <v>3980</v>
@@ -5523,7 +5569,7 @@
         <v>11</v>
       </c>
       <c r="G99" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H99" s="14">
         <v>3980</v>
@@ -5679,7 +5725,7 @@
         <v>14</v>
       </c>
       <c r="G103" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H103" s="14">
         <v>3980</v>
@@ -6334,7 +6380,7 @@
         <v>22</v>
       </c>
       <c r="G120" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H120" s="14">
         <v>3980</v>
@@ -6519,7 +6565,7 @@
         <v>22</v>
       </c>
       <c r="G125" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H125" s="14">
         <v>3980</v>
@@ -6710,7 +6756,7 @@
         <v>21</v>
       </c>
       <c r="G130" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H130" s="12">
         <v>99</v>
@@ -7022,7 +7068,7 @@
         <v>19</v>
       </c>
       <c r="G138" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H138" s="12">
         <v>99</v>
@@ -7330,7 +7376,7 @@
         <v>8</v>
       </c>
       <c r="G146" s="13" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H146" s="12">
         <v>3971</v>
@@ -7659,7 +7705,7 @@
         <v>29</v>
       </c>
       <c r="G155" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H155" s="14">
         <v>3980</v>
@@ -7774,7 +7820,7 @@
         <v>3</v>
       </c>
       <c r="G158" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H158" s="12">
         <v>3971</v>
@@ -7928,7 +7974,7 @@
         <v>13</v>
       </c>
       <c r="G162" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H162" s="12">
         <v>99</v>
@@ -8123,7 +8169,7 @@
         <v>21</v>
       </c>
       <c r="G167" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H167" s="12">
         <v>3971</v>
@@ -8394,7 +8440,7 @@
         <v>21</v>
       </c>
       <c r="G174" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H174" s="12">
         <v>99</v>
@@ -8470,7 +8516,7 @@
         <v>1</v>
       </c>
       <c r="G176" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H176" s="14">
         <v>3980</v>
@@ -9148,7 +9194,7 @@
         <v>2007</v>
       </c>
       <c r="E194" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F194" s="12"/>
       <c r="G194" s="13" t="s">
@@ -9762,7 +9808,7 @@
         <v>5</v>
       </c>
       <c r="G210" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H210" s="14">
         <v>3980</v>
@@ -10000,7 +10046,7 @@
         <v>22</v>
       </c>
       <c r="G216" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H216" s="12">
         <v>3971</v>
@@ -10322,7 +10368,7 @@
         <v>13</v>
       </c>
       <c r="G224" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H224" s="14">
         <v>3971</v>
@@ -10404,7 +10450,7 @@
         <v>24</v>
       </c>
       <c r="G226" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H226" s="12">
         <v>99</v>
@@ -10864,7 +10910,7 @@
         <v>12</v>
       </c>
       <c r="G238" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H238" s="12">
         <v>99</v>
@@ -11414,7 +11460,7 @@
         <v>12</v>
       </c>
       <c r="G252" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H252" s="12">
         <v>3971</v>
@@ -11453,7 +11499,7 @@
         <v>25</v>
       </c>
       <c r="G253" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H253" s="12">
         <v>3971</v>
@@ -11654,7 +11700,7 @@
         <v>5</v>
       </c>
       <c r="G258" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H258" s="12">
         <v>3971</v>
@@ -11886,7 +11932,7 @@
         <v>12</v>
       </c>
       <c r="G264" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H264" s="12">
         <v>99</v>
@@ -11925,7 +11971,7 @@
         <v>10</v>
       </c>
       <c r="G265" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H265" s="14">
         <v>3971</v>
@@ -12288,7 +12334,7 @@
         <v>31</v>
       </c>
       <c r="G274" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H274" s="14">
         <v>3980</v>
@@ -12366,7 +12412,7 @@
         <v>22</v>
       </c>
       <c r="G276" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H276" s="12">
         <v>99</v>
@@ -12733,7 +12779,7 @@
         <v>21</v>
       </c>
       <c r="G285" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H285" s="12">
         <v>99</v>
@@ -12998,7 +13044,7 @@
         <v>6</v>
       </c>
       <c r="G292" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H292" s="14">
         <v>3971</v>
@@ -13076,7 +13122,7 @@
         <v>30</v>
       </c>
       <c r="G294" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H294" s="14">
         <v>3980</v>
@@ -13154,7 +13200,7 @@
         <v>8</v>
       </c>
       <c r="G296" s="13" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H296" s="12">
         <v>3971</v>
@@ -13710,7 +13756,7 @@
         <v>4</v>
       </c>
       <c r="G310" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H310" s="14">
         <v>3971</v>
@@ -13790,7 +13836,7 @@
         <v>7</v>
       </c>
       <c r="G312" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H312" s="12">
         <v>3971</v>
@@ -14053,7 +14099,7 @@
         <v>22</v>
       </c>
       <c r="G319" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H319" s="12">
         <v>99</v>
@@ -14314,7 +14360,7 @@
         <v>26</v>
       </c>
       <c r="G326" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H326" s="12">
         <v>3971</v>
@@ -14390,7 +14436,7 @@
         <v>30</v>
       </c>
       <c r="G328" s="13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H328" s="14">
         <v>3962</v>
@@ -14462,7 +14508,7 @@
         <v>22</v>
       </c>
       <c r="G330" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H330" s="14">
         <v>3980</v>
@@ -14836,7 +14882,7 @@
         <v>21</v>
       </c>
       <c r="G340" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H340" s="12">
         <v>99</v>
@@ -14951,7 +14997,7 @@
         <v>5</v>
       </c>
       <c r="G343" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H343" s="14">
         <v>3980</v>
@@ -15027,7 +15073,7 @@
         <v>11</v>
       </c>
       <c r="G345" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H345" s="14">
         <v>3971</v>
@@ -15173,7 +15219,7 @@
         <v>4</v>
       </c>
       <c r="G349" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H349" s="14">
         <v>3971</v>
@@ -15288,7 +15334,7 @@
         <v>11</v>
       </c>
       <c r="G352" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H352" s="14">
         <v>3971</v>
@@ -16155,7 +16201,7 @@
         <v>12</v>
       </c>
       <c r="G375" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H375" s="14">
         <v>3980</v>
@@ -16379,7 +16425,7 @@
         <v>21</v>
       </c>
       <c r="G381" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H381" s="12">
         <v>3971</v>
@@ -16490,7 +16536,7 @@
         <v>24</v>
       </c>
       <c r="G384" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H384" s="12">
         <v>3971</v>
@@ -16823,7 +16869,7 @@
         <v>11</v>
       </c>
       <c r="G393" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H393" s="14">
         <v>3971</v>
@@ -16897,7 +16943,7 @@
         <v>11</v>
       </c>
       <c r="G395" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H395" s="14">
         <v>3980</v>
@@ -16971,7 +17017,7 @@
         <v>21</v>
       </c>
       <c r="G397" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H397" s="12">
         <v>99</v>
@@ -17216,7 +17262,7 @@
       </c>
       <c r="F404" s="12"/>
       <c r="G404" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H404" s="14">
         <v>3980</v>
@@ -17288,7 +17334,7 @@
         <v>16</v>
       </c>
       <c r="G406" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H406" s="12">
         <v>99</v>
@@ -17325,7 +17371,7 @@
         <v>11</v>
       </c>
       <c r="G407" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H407" s="14">
         <v>3971</v>
@@ -17471,7 +17517,7 @@
         <v>11</v>
       </c>
       <c r="G411" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H411" s="14">
         <v>3980</v>
@@ -17543,7 +17589,7 @@
         <v>15</v>
       </c>
       <c r="G413" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H413" s="14">
         <v>3980</v>
@@ -17580,7 +17626,7 @@
         <v>5</v>
       </c>
       <c r="G414" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H414" s="14">
         <v>3980</v>
@@ -17691,7 +17737,7 @@
         <v>7</v>
       </c>
       <c r="G417" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H417" s="14">
         <v>3980</v>
@@ -17804,7 +17850,7 @@
         <v>22</v>
       </c>
       <c r="G420" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H420" s="14">
         <v>3980</v>
@@ -17841,7 +17887,7 @@
         <v>13</v>
       </c>
       <c r="G421" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H421" s="12">
         <v>3971</v>
@@ -18071,7 +18117,7 @@
         <v>14</v>
       </c>
       <c r="G427" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H427" s="14">
         <v>3980</v>
@@ -18219,7 +18265,7 @@
         <v>3</v>
       </c>
       <c r="G431" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H431" s="14">
         <v>3980</v>
@@ -18256,7 +18302,7 @@
         <v>21</v>
       </c>
       <c r="G432" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H432" s="12">
         <v>99</v>
@@ -18293,7 +18339,7 @@
         <v>3</v>
       </c>
       <c r="G433" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H433" s="14">
         <v>3980</v>
@@ -18330,7 +18376,7 @@
         <v>22</v>
       </c>
       <c r="G434" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H434" s="14">
         <v>3980</v>
@@ -18404,7 +18450,7 @@
         <v>5</v>
       </c>
       <c r="G436" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H436" s="14">
         <v>3980</v>
@@ -18589,7 +18635,7 @@
         <v>17</v>
       </c>
       <c r="G441" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H441" s="12">
         <v>99</v>
@@ -18624,7 +18670,7 @@
         <v>22</v>
       </c>
       <c r="G442" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H442" s="12">
         <v>99</v>
@@ -18661,7 +18707,7 @@
         <v>15</v>
       </c>
       <c r="G443" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H443" s="12">
         <v>99</v>
@@ -18850,7 +18896,7 @@
         <v>28</v>
       </c>
       <c r="G448" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H448" s="14">
         <v>3971</v>
@@ -19037,7 +19083,7 @@
         <v>25</v>
       </c>
       <c r="G453" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H453" s="14">
         <v>3980</v>
@@ -19306,7 +19352,7 @@
         <v>22</v>
       </c>
       <c r="G460" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H460" s="12">
         <v>99</v>
@@ -19343,7 +19389,7 @@
         <v>26</v>
       </c>
       <c r="G461" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H461" s="14">
         <v>3971</v>
@@ -19380,7 +19426,7 @@
         <v>4</v>
       </c>
       <c r="G462" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H462" s="14">
         <v>3971</v>
@@ -19643,7 +19689,7 @@
         <v>3</v>
       </c>
       <c r="G469" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H469" s="12">
         <v>3971</v>
@@ -19793,7 +19839,7 @@
         <v>3</v>
       </c>
       <c r="G473" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H473" s="14">
         <v>3980</v>
@@ -20011,7 +20057,7 @@
         <v>11</v>
       </c>
       <c r="G479" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H479" s="14">
         <v>3971</v>
@@ -20046,7 +20092,7 @@
         <v>21</v>
       </c>
       <c r="G480" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H480" s="12">
         <v>3971</v>
@@ -20194,7 +20240,7 @@
         <v>9</v>
       </c>
       <c r="G484" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H484" s="14">
         <v>3980</v>
@@ -20231,7 +20277,7 @@
         <v>30</v>
       </c>
       <c r="G485" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H485" s="12">
         <v>3971</v>
@@ -20494,7 +20540,7 @@
         <v>10</v>
       </c>
       <c r="G492" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H492" s="12">
         <v>99</v>
@@ -20564,7 +20610,7 @@
         <v>21</v>
       </c>
       <c r="G494" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H494" s="12">
         <v>99</v>
@@ -20599,7 +20645,7 @@
         <v>11</v>
       </c>
       <c r="G495" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H495" s="14">
         <v>3971</v>
@@ -20942,7 +20988,7 @@
         <v>17</v>
       </c>
       <c r="G504" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H504" s="12">
         <v>3971</v>
@@ -21053,7 +21099,7 @@
         <v>22</v>
       </c>
       <c r="G507" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H507" s="14">
         <v>3980</v>
@@ -21468,7 +21514,7 @@
         <v>15</v>
       </c>
       <c r="G518" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H518" s="12">
         <v>99</v>
@@ -21725,7 +21771,7 @@
         <v>10</v>
       </c>
       <c r="G525" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H525" s="14">
         <v>3980</v>
@@ -21830,7 +21876,7 @@
         <v>2007</v>
       </c>
       <c r="E528" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F528" s="12"/>
       <c r="G528" s="13" t="s">
@@ -22138,7 +22184,7 @@
         <v>12</v>
       </c>
       <c r="G536" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H536" s="14">
         <v>3980</v>
@@ -22175,7 +22221,7 @@
         <v>3</v>
       </c>
       <c r="G537" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H537" s="14">
         <v>3980</v>
@@ -22397,7 +22443,7 @@
         <v>15</v>
       </c>
       <c r="G543" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H543" s="12">
         <v>99</v>
@@ -22576,7 +22622,7 @@
         <v>3</v>
       </c>
       <c r="G548" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H548" s="14">
         <v>3971</v>
@@ -22841,7 +22887,7 @@
         <v>21</v>
       </c>
       <c r="G555" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H555" s="12">
         <v>99</v>
@@ -23178,7 +23224,7 @@
         <v>13</v>
       </c>
       <c r="G564" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H564" s="14">
         <v>3980</v>
@@ -23910,7 +23956,7 @@
         <v>3</v>
       </c>
       <c r="G584" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H584" s="12">
         <v>3971</v>
@@ -23945,7 +23991,7 @@
         <v>1</v>
       </c>
       <c r="G585" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H585" s="12">
         <v>3971</v>
@@ -24149,7 +24195,7 @@
         <v>1985</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E5" s="12">
         <v>80</v>
@@ -24299,7 +24345,7 @@
         <v>2008</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E10" s="12">
         <v>62</v>
@@ -24731,7 +24777,7 @@
         <v>2008</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E25" s="16">
         <v>55</v>
